--- a/battery_data.xlsx
+++ b/battery_data.xlsx
@@ -7,7 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Master" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Alpha" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="A" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="E" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="F" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,8 +38,13 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font/>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +55,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+        <bgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -69,6 +109,40 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -435,6 +509,5078 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L78"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Source Battery</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Source Cell</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Capacity (Ah)</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>IR (mOhm)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>End Voltage (V)</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Duration (min)</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Session ID</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Used</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>Assigned To</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>6.435</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>20260328_0839</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>6.451</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>20260328_0839</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>6.428</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>206.8</v>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>20260328_0839</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>6.454</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>111</v>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>20260328_0839</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>6.427</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>20260328_0839</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>6.412</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>192</v>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>20260328_0839</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>6.432</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>173.8</v>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>20260328_0839</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>6.428</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>20260404_1826</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>6.435</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>20260404_1826</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>6.557</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>20260404_1826</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>6.435</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>124.8</v>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>20260404_1826</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>6.479</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>20260404_1826</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>6.534</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>20260404_1826</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>6.411</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>20260404_1826</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>6.435</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>137.8</v>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>20260407_1934+20260407_1935</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>6.683</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>20260407_1934+20260407_1935</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n">
+        <v>6.426</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>20260407_1934+20260407_1935</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L18" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>6.571</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>20260407_1934+20260407_1935</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>6.434</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>20260407_1934+20260407_1935</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>6.419</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>20260407_1934+20260407_1935</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>6.586</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>20260407_1934+20260407_1935</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="K22" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L22" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>6.426</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>20260410_2305</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>6.427</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>20260410_2305</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>6.451</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>20260410_2305</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>6.763</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>20260410_2305</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>6.437</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>125.3</v>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>20260410_2305</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>6.428</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>162.8</v>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>20260410_2305</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>6.411</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>20260410_2305</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>6.768</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>20260412_1918</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>6.444</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>20260412_1918</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>6.625</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>20260412_1918</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>6.406</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>20260412_1918</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>6.581</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>20260412_1918</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="K34" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L34" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>6.964</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>20260412_1918</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>20260412_1918</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>6.491</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>20260413_1943</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>6.431</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>151.3</v>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>20260413_1943</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>6.474</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>20260413_1943</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>6.439</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>147.8</v>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>20260413_1943</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>6.423</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>20260413_1943</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>6.536</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>20260413_1943</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>6.533</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>20260413_1943</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>6.588</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>20260417_0743</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>6.423</v>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>146.8</v>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>20260417_0743</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>6.479</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>20260417_0743</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>6.404</v>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>137.7</v>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>20260417_0743</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>6.426</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>20260417_0743</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>6.556</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>20260417_0743</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>6.491</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>20260417_0743</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L50" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>6.423</v>
+      </c>
+      <c r="G51" s="7" t="n">
+        <v>133</v>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>20260418_1412+20260418_1413</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>6.749</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>20260418_1412+20260418_1413</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L52" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>6.648</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>20260418_1412+20260418_1413</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>6.406</v>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>20260418_1412+20260418_1413</t>
+        </is>
+      </c>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>6.452</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>20260418_1412+20260418_1413</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L55" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E56" s="14" t="n"/>
+      <c r="F56" s="14" t="n">
+        <v>6.441</v>
+      </c>
+      <c r="G56" s="14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H56" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>20260418_1412+20260418_1413</t>
+        </is>
+      </c>
+      <c r="J56" s="14" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="K56" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L56" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>6.435</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>20260418_1412+20260418_1413</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L57" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>20260420_0919</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L58" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G59" s="7" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>20260420_0919</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>6.471</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>20260420_0919</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L60" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="D61" s="14" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E61" s="14" t="n"/>
+      <c r="F61" s="14" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G61" s="14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H61" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="I61" s="14" t="inlineStr">
+        <is>
+          <t>20260420_0919</t>
+        </is>
+      </c>
+      <c r="J61" s="14" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="K61" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L61" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>6.473</v>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>20260420_0919</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D63" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="F63" s="15" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="G63" s="15" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H63" s="15" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="I63" s="15" t="inlineStr">
+        <is>
+          <t>20260420_0919</t>
+        </is>
+      </c>
+      <c r="J63" s="15" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="K63" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L63" s="15" t="inlineStr">
+        <is>
+          <t>Disqualified</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>6.519</v>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>20260420_0919</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E65" s="7" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F65" s="7" t="n">
+        <v>6.429</v>
+      </c>
+      <c r="G65" s="7" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>20260421_2238</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>6.488</v>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>20260421_2238</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L66" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="D67" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E67" s="14" t="n"/>
+      <c r="F67" s="14" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="G67" s="14" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H67" s="14" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="I67" s="14" t="inlineStr">
+        <is>
+          <t>20260421_2238</t>
+        </is>
+      </c>
+      <c r="J67" s="14" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="K67" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L67" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>6.713</v>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>20260421_2238</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L68" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E69" s="7" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F69" s="7" t="n">
+        <v>6.414</v>
+      </c>
+      <c r="G69" s="7" t="n">
+        <v>142.3</v>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>20260421_2238</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>6.427</v>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>20260421_2238</t>
+        </is>
+      </c>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E71" s="7" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>6.405</v>
+      </c>
+      <c r="G71" s="7" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>20260421_2238</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>6.465</v>
+      </c>
+      <c r="G72" s="6" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>20260424_0743+20260424_0744</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L72" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F73" s="7" t="n">
+        <v>6.414</v>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>141.3</v>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>20260424_0743+20260424_0744</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="16" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="D74" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="16" t="n"/>
+      <c r="F74" s="16" t="n">
+        <v>6.597</v>
+      </c>
+      <c r="G74" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H74" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
+        <is>
+          <t>20260424_0743+20260424_0744</t>
+        </is>
+      </c>
+      <c r="J74" s="16" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L74" s="13" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>6.423</v>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>145.1</v>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>20260424_0743+20260424_0744</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>144.1</v>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>20260424_0743+20260424_0744</t>
+        </is>
+      </c>
+      <c r="J76" s="7" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="K76" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L76" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="16" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="16" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C77" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="D77" s="16" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E77" s="16" t="n"/>
+      <c r="F77" s="16" t="n">
+        <v>6.474</v>
+      </c>
+      <c r="G77" s="16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H77" s="16" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="I77" s="16" t="inlineStr">
+        <is>
+          <t>20260424_0743+20260424_0744</t>
+        </is>
+      </c>
+      <c r="J77" s="16" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="K77" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L77" s="13" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="F78" s="7" t="n">
+        <v>6.401</v>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>20260424_0743+20260424_0744</t>
+        </is>
+      </c>
+      <c r="J78" s="7" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="K78" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AC9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 1</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 2</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 3</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 4</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 5</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 6</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 7</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 8</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 9</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 10</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 11</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 12</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 13</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 14</t>
+        </is>
+      </c>
+      <c r="P1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 15</t>
+        </is>
+      </c>
+      <c r="Q1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 16</t>
+        </is>
+      </c>
+      <c r="R1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 17</t>
+        </is>
+      </c>
+      <c r="S1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 18</t>
+        </is>
+      </c>
+      <c r="T1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 19</t>
+        </is>
+      </c>
+      <c r="U1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 20</t>
+        </is>
+      </c>
+      <c r="V1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 21</t>
+        </is>
+      </c>
+      <c r="W1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 22</t>
+        </is>
+      </c>
+      <c r="X1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 23</t>
+        </is>
+      </c>
+      <c r="Y1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 24</t>
+        </is>
+      </c>
+      <c r="Z1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 25</t>
+        </is>
+      </c>
+      <c r="AA1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 26</t>
+        </is>
+      </c>
+      <c r="AB1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 27</t>
+        </is>
+      </c>
+      <c r="AC1" s="5" t="inlineStr">
+        <is>
+          <t>Cell 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Discharge Capacity (Ah)</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K2" s="6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L2" s="6" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M2" s="6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N2" s="6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O2" s="6" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="S2" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T2" s="6" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="U2" s="6" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="V2" s="6" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="W2" s="6" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="X2" s="6" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="Y2" s="6" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="Z2" s="6" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AA2" s="6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB2" s="6" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AC2" s="6" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Internal Resistance (mOhm)</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="L3" s="6" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="M3" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="N3" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="O3" s="6" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="S3" s="6" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="T3" s="6" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="U3" s="6" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="V3" s="6" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="W3" s="6" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="X3" s="6" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="Y3" s="6" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="Z3" s="6" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AA3" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB3" s="6" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="AC3" s="6" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>End Voltage (V)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>6.426</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>6.406</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>6.406</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>6.428</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>6.427</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>6.444</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>6.401</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>6.405</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>6.429</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>6.411</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>6.411</v>
+      </c>
+      <c r="N4" s="6" t="n">
+        <v>6.435</v>
+      </c>
+      <c r="O4" s="6" t="n">
+        <v>6.437</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v>6.435</v>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v>6.519</v>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v>6.423</v>
+      </c>
+      <c r="S4" s="6" t="n">
+        <v>6.419</v>
+      </c>
+      <c r="T4" s="6" t="n">
+        <v>6.435</v>
+      </c>
+      <c r="U4" s="6" t="n">
+        <v>6.404</v>
+      </c>
+      <c r="V4" s="6" t="n">
+        <v>6.426</v>
+      </c>
+      <c r="W4" s="6" t="n">
+        <v>6.414</v>
+      </c>
+      <c r="X4" s="6" t="n">
+        <v>6.414</v>
+      </c>
+      <c r="Y4" s="6" t="n">
+        <v>6.473</v>
+      </c>
+      <c r="Z4" s="6" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="AA4" s="6" t="n">
+        <v>6.423</v>
+      </c>
+      <c r="AB4" s="6" t="n">
+        <v>6.423</v>
+      </c>
+      <c r="AC4" s="6" t="n">
+        <v>6.439</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Duration (min)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O5" s="6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S5" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T5" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U5" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V5" s="6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W5" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X5" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y5" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z5" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA5" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB5" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC5" s="6" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="T6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="U6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="V6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="W6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="X6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Y6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AA6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC6" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Session ID</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>20260417_0743</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>20260418_1412+20260418_1413</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>20260412_1918</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>20260404_1826</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>20260420_0919</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>20260421_2238</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>20260412_1918</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>20260424_0743+20260424_0744</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>20260421_2238</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>20260421_2238</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>20260404_1826</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>20260410_2305</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>20260404_1826</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>20260410_2305</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>20260404_1826</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>20260420_0919</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>20260418_1412+20260418_1413</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>20260407_1934+20260407_1935</t>
+        </is>
+      </c>
+      <c r="T7" s="6" t="inlineStr">
+        <is>
+          <t>20260407_1934+20260407_1935</t>
+        </is>
+      </c>
+      <c r="U7" s="6" t="inlineStr">
+        <is>
+          <t>20260417_0743</t>
+        </is>
+      </c>
+      <c r="V7" s="6" t="inlineStr">
+        <is>
+          <t>20260410_2305</t>
+        </is>
+      </c>
+      <c r="W7" s="6" t="inlineStr">
+        <is>
+          <t>20260424_0743+20260424_0744</t>
+        </is>
+      </c>
+      <c r="X7" s="6" t="inlineStr">
+        <is>
+          <t>20260421_2238</t>
+        </is>
+      </c>
+      <c r="Y7" s="6" t="inlineStr">
+        <is>
+          <t>20260420_0919</t>
+        </is>
+      </c>
+      <c r="Z7" s="6" t="inlineStr">
+        <is>
+          <t>20260424_0743+20260424_0744</t>
+        </is>
+      </c>
+      <c r="AA7" s="6" t="inlineStr">
+        <is>
+          <t>20260424_0743+20260424_0744</t>
+        </is>
+      </c>
+      <c r="AB7" s="6" t="inlineStr">
+        <is>
+          <t>20260417_0743</t>
+        </is>
+      </c>
+      <c r="AC7" s="6" t="inlineStr">
+        <is>
+          <t>20260413_1943</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Channel Used</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="T8" s="6" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="U8" s="6" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="V8" s="6" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="W8" s="6" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="X8" s="6" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="Y8" s="6" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="Z8" s="6" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="AA8" s="6" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="AB8" s="6" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="AC8" s="6" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Source (Battery-Cell)</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>E-26</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>F-4</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>E-11</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>D-15</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>F-9</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>F-20</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>E-9</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>F-28</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>F-21</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>F-15</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>D-21</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>E-7</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>D-18</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>E-5</t>
+        </is>
+      </c>
+      <c r="P9" s="9" t="inlineStr">
+        <is>
+          <t>D-16</t>
+        </is>
+      </c>
+      <c r="Q9" s="9" t="inlineStr">
+        <is>
+          <t>F-14</t>
+        </is>
+      </c>
+      <c r="R9" s="9" t="inlineStr">
+        <is>
+          <t>F-1</t>
+        </is>
+      </c>
+      <c r="S9" s="9" t="inlineStr">
+        <is>
+          <t>D-27</t>
+        </is>
+      </c>
+      <c r="T9" s="9" t="inlineStr">
+        <is>
+          <t>D-22</t>
+        </is>
+      </c>
+      <c r="U9" s="9" t="inlineStr">
+        <is>
+          <t>E-25</t>
+        </is>
+      </c>
+      <c r="V9" s="9" t="inlineStr">
+        <is>
+          <t>E-1</t>
+        </is>
+      </c>
+      <c r="W9" s="9" t="inlineStr">
+        <is>
+          <t>F-23</t>
+        </is>
+      </c>
+      <c r="X9" s="9" t="inlineStr">
+        <is>
+          <t>F-19</t>
+        </is>
+      </c>
+      <c r="Y9" s="9" t="inlineStr">
+        <is>
+          <t>F-12</t>
+        </is>
+      </c>
+      <c r="Z9" s="9" t="inlineStr">
+        <is>
+          <t>F-26</t>
+        </is>
+      </c>
+      <c r="AA9" s="9" t="inlineStr">
+        <is>
+          <t>F-25</t>
+        </is>
+      </c>
+      <c r="AB9" s="9" t="inlineStr">
+        <is>
+          <t>E-23</t>
+        </is>
+      </c>
+      <c r="AC9" s="9" t="inlineStr">
+        <is>
+          <t>E-18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -857,4 +6003,2605 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AC8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 1</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 2</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 3</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 4</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 5</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 6</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 7</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 8</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 9</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 10</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 11</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 12</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 13</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 14</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 15</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 16</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 17</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 18</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 19</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 20</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 21</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 22</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 23</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 24</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 25</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 26</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 27</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Discharge Capacity (Ah)</t>
+        </is>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T2" s="4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U2" s="4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="X2" s="4" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="Y2" s="4" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z2" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA2" s="4" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AB2" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC2" s="4" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Internal Resistance (mOhm)</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="Y3" s="4" t="n"/>
+      <c r="Z3" s="4" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="AA3" s="4" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AB3" s="4" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AC3" s="4" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>End Voltage (V)</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>6.428</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>6.435</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>6.557</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>6.435</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>6.479</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>6.534</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>6.411</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>6.435</v>
+      </c>
+      <c r="X4" s="4" t="n">
+        <v>6.683</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <v>6.426</v>
+      </c>
+      <c r="Z4" s="4" t="n">
+        <v>6.571</v>
+      </c>
+      <c r="AA4" s="4" t="n">
+        <v>6.434</v>
+      </c>
+      <c r="AB4" s="4" t="n">
+        <v>6.419</v>
+      </c>
+      <c r="AC4" s="4" t="n">
+        <v>6.586</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Duration (min)</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>124.8</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>137.8</v>
+      </c>
+      <c r="X5" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y5" s="4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Z5" s="4" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AA5" s="4" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="AB5" s="4" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="AC5" s="4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Session ID</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>20260404_1826</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>20260404_1826</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>20260404_1826</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>20260404_1826</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>20260404_1826</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>20260404_1826</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>20260404_1826</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr">
+        <is>
+          <t>20260407_1934+20260407_1935</t>
+        </is>
+      </c>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>20260407_1934+20260407_1935</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>20260407_1934+20260407_1935</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>20260407_1934+20260407_1935</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr">
+        <is>
+          <t>20260407_1934+20260407_1935</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>20260407_1934+20260407_1935</t>
+        </is>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>20260407_1934+20260407_1935</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Channel Used</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AC8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 1</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 2</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 3</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 4</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 5</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 6</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 7</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 8</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 9</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 10</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 11</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 12</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 13</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 14</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 15</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 16</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 17</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 18</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 19</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 20</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 21</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 22</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 23</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 24</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 25</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 26</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 27</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Discharge Capacity (Ah)</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="T2" s="4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U2" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="X2" s="4" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="Y2" s="4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="Z2" s="4" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AA2" s="4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB2" s="4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC2" s="4" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Internal Resistance (mOhm)</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z3" s="4" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AA3" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB3" s="4" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="AC3" s="4" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>End Voltage (V)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>6.426</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>6.427</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>6.451</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>6.763</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>6.437</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>6.428</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>6.411</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>6.768</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>6.444</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>6.625</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>6.406</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>6.581</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>6.964</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>6.491</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>6.431</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>6.474</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>6.439</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>6.423</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>6.536</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>6.533</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>6.588</v>
+      </c>
+      <c r="X4" s="4" t="n">
+        <v>6.423</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <v>6.479</v>
+      </c>
+      <c r="Z4" s="4" t="n">
+        <v>6.404</v>
+      </c>
+      <c r="AA4" s="4" t="n">
+        <v>6.426</v>
+      </c>
+      <c r="AB4" s="4" t="n">
+        <v>6.556</v>
+      </c>
+      <c r="AC4" s="4" t="n">
+        <v>6.491</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Duration (min)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>125.3</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>162.8</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>151.3</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>147.8</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="X5" s="4" t="n">
+        <v>146.8</v>
+      </c>
+      <c r="Y5" s="4" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="Z5" s="4" t="n">
+        <v>137.7</v>
+      </c>
+      <c r="AA5" s="4" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="AB5" s="4" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="AC5" s="4" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Session ID</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>20260410_2305</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>20260410_2305</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>20260410_2305</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>20260410_2305</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>20260410_2305</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>20260410_2305</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>20260410_2305</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>20260412_1918</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>20260412_1918</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>20260412_1918</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>20260412_1918</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>20260412_1918</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>20260412_1918</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>20260412_1918</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>20260413_1943</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>20260413_1943</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>20260413_1943</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>20260413_1943</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>20260413_1943</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>20260413_1943</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>20260413_1943</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr">
+        <is>
+          <t>20260417_0743</t>
+        </is>
+      </c>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>20260417_0743</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>20260417_0743</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>20260417_0743</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr">
+        <is>
+          <t>20260417_0743</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>20260417_0743</t>
+        </is>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>20260417_0743</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Channel Used</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AC8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 1</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 2</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 3</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 4</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 5</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 6</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 7</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 8</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 9</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 10</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 11</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 12</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 13</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 14</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 15</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 16</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 17</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 18</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 19</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 20</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 21</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 22</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 23</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 24</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 25</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 26</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 27</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>Cell 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Discharge Capacity (Ah)</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T2" s="4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U2" s="4" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X2" s="4" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="Y2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA2" s="4" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AB2" s="4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AC2" s="4" t="n">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Internal Resistance (mOhm)</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="R3" s="4" t="n"/>
+      <c r="S3" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="Y3" s="4" t="n"/>
+      <c r="Z3" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA3" s="4" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AB3" s="4" t="n"/>
+      <c r="AC3" s="4" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>End Voltage (V)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>6.423</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>6.749</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>6.648</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>6.406</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>6.452</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>6.441</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>6.435</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>6.471</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>6.473</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>6.519</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>6.429</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>6.488</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>6.713</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>6.414</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>6.427</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>6.405</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>6.465</v>
+      </c>
+      <c r="X4" s="4" t="n">
+        <v>6.414</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <v>6.597</v>
+      </c>
+      <c r="Z4" s="4" t="n">
+        <v>6.423</v>
+      </c>
+      <c r="AA4" s="4" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="AB4" s="4" t="n">
+        <v>6.474</v>
+      </c>
+      <c r="AC4" s="4" t="n">
+        <v>6.401</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Duration (min)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>133</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>142.3</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="X5" s="4" t="n">
+        <v>141.3</v>
+      </c>
+      <c r="Y5" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z5" s="4" t="n">
+        <v>145.1</v>
+      </c>
+      <c r="AA5" s="4" t="n">
+        <v>144.1</v>
+      </c>
+      <c r="AB5" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC5" s="4" t="n">
+        <v>104.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Session ID</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>20260418_1412+20260418_1413</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>20260418_1412+20260418_1413</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>20260418_1412+20260418_1413</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>20260418_1412+20260418_1413</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>20260418_1412+20260418_1413</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>20260418_1412+20260418_1413</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>20260418_1412+20260418_1413</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>20260420_0919</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>20260420_0919</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>20260420_0919</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>20260420_0919</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>20260420_0919</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>20260420_0919</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>20260420_0919</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>20260421_2238</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>20260421_2238</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>20260421_2238</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>20260421_2238</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>20260421_2238</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>20260421_2238</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>20260421_2238</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr">
+        <is>
+          <t>20260424_0743+20260424_0744</t>
+        </is>
+      </c>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>20260424_0743+20260424_0744</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>20260424_0743+20260424_0744</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>20260424_0743+20260424_0744</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr">
+        <is>
+          <t>20260424_0743+20260424_0744</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>20260424_0743+20260424_0744</t>
+        </is>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>20260424_0743+20260424_0744</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Channel Used</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr">
+        <is>
+          <t>CH1</t>
+        </is>
+      </c>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>CH2</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>CH5</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="inlineStr">
+        <is>
+          <t>CH6</t>
+        </is>
+      </c>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>CH7</t>
+        </is>
+      </c>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>CH8</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>